--- a/MAJSushiConfig/ig/FRImagingSeriesLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRImagingSeriesLMCDAFHIR.xlsx
@@ -29,7 +29,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/ConceptMap/FRImagingSeriesLMCDAFHIR</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/ConceptMap/FRImagingSeriesLMCDAFHIR</t>
   </si>
   <si>
     <t>Version</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:25:17+00:00</t>
+    <t>2026-09-07T11:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -110,7 +110,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMSeries</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMSeries|0.1.0</t>
   </si>
   <si>
     <t/>
@@ -161,7 +161,7 @@
     <t>FRLMSeries.instanceSOP</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMSOPInstance</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMSOPInstance|0.1.0</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-dicom-sop-instance-observation|0.1.0</t>
@@ -179,7 +179,7 @@
     <t>Observation.code</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMEndpoint</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMEndpoint|0.1.0</t>
   </si>
   <si>
     <t>FRLMEndpoint.connectionType</t>

--- a/MAJSushiConfig/ig/FRImagingSeriesLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRImagingSeriesLMCDAFHIR.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:26:50+00:00</t>
+    <t>2026-09-07T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
